--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/30.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/30.xlsx
@@ -426,13 +426,13 @@
         <v>-12.04811738811971</v>
       </c>
       <c r="E2">
-        <v>-7.16550159699857</v>
+        <v>-9.934704208955063</v>
       </c>
       <c r="F2">
-        <v>-4.039663840681537</v>
+        <v>-4.066037402051867</v>
       </c>
       <c r="G2">
-        <v>-11.43781018811979</v>
+        <v>-12.10453419645577</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-12.06595465204242</v>
       </c>
       <c r="E3">
-        <v>-8.070725437235843</v>
+        <v>-10.19139170113184</v>
       </c>
       <c r="F3">
-        <v>-3.933367735554304</v>
+        <v>-3.925825450351814</v>
       </c>
       <c r="G3">
-        <v>-11.21884077451578</v>
+        <v>-11.77316183015689</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-12.07973575027723</v>
       </c>
       <c r="E4">
-        <v>-9.114828518340351</v>
+        <v>-10.45607194993216</v>
       </c>
       <c r="F4">
-        <v>-3.639479548389095</v>
+        <v>-3.852021228231989</v>
       </c>
       <c r="G4">
-        <v>-10.68680300089951</v>
+        <v>-12.1218516601717</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-12.08949865689763</v>
       </c>
       <c r="E5">
-        <v>-8.897932727268973</v>
+        <v>-10.68322926310492</v>
       </c>
       <c r="F5">
-        <v>-3.658691045194821</v>
+        <v>-3.883669004855945</v>
       </c>
       <c r="G5">
-        <v>-11.62415086488875</v>
+        <v>-11.22011202400286</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-12.07934236925317</v>
       </c>
       <c r="E6">
-        <v>-10.43515040001672</v>
+        <v>-12.39200817363326</v>
       </c>
       <c r="F6">
-        <v>-3.531034658219001</v>
+        <v>-3.487083968928667</v>
       </c>
       <c r="G6">
-        <v>-11.12096118510169</v>
+        <v>-11.16895085323896</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-12.04757057703345</v>
       </c>
       <c r="E7">
-        <v>-11.27921719878041</v>
+        <v>-12.86334986224762</v>
       </c>
       <c r="F7">
-        <v>-3.618833319241721</v>
+        <v>-3.363437708549799</v>
       </c>
       <c r="G7">
-        <v>-11.12400026590674</v>
+        <v>-11.12725453217184</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-11.98968758480081</v>
       </c>
       <c r="E8">
-        <v>-11.93051138751157</v>
+        <v>-13.77325614460883</v>
       </c>
       <c r="F8">
-        <v>-3.166942333666534</v>
+        <v>-3.331623430077881</v>
       </c>
       <c r="G8">
-        <v>-11.17338036317051</v>
+        <v>-11.39795784091805</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-11.90016257071371</v>
       </c>
       <c r="E9">
-        <v>-13.02618473061543</v>
+        <v>-14.44457524540191</v>
       </c>
       <c r="F9">
-        <v>-2.923899337685159</v>
+        <v>-3.225447438224055</v>
       </c>
       <c r="G9">
-        <v>-11.59346872883079</v>
+        <v>-11.29327508042075</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-11.7841670279037</v>
       </c>
       <c r="E10">
-        <v>-13.16454772544579</v>
+        <v>-13.68904464196219</v>
       </c>
       <c r="F10">
-        <v>-2.877099064529196</v>
+        <v>-3.101091266980987</v>
       </c>
       <c r="G10">
-        <v>-10.14850167512293</v>
+        <v>-10.14202955859366</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-11.62903472963521</v>
       </c>
       <c r="E11">
-        <v>-14.64480625212506</v>
+        <v>-15.71535562143437</v>
       </c>
       <c r="F11">
-        <v>-2.572524109500471</v>
+        <v>-2.92998618136093</v>
       </c>
       <c r="G11">
-        <v>-9.877040251448234</v>
+        <v>-11.05165491423704</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-11.44684548767364</v>
       </c>
       <c r="E12">
-        <v>-14.57888525599541</v>
+        <v>-15.43119387745305</v>
       </c>
       <c r="F12">
-        <v>-2.621724163022344</v>
+        <v>-2.645109803170777</v>
       </c>
       <c r="G12">
-        <v>-9.915313468427749</v>
+        <v>-10.03197709323167</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-11.22191807177587</v>
       </c>
       <c r="E13">
-        <v>-14.71748825994817</v>
+        <v>-16.77395434783743</v>
       </c>
       <c r="F13">
-        <v>-2.508386106603913</v>
+        <v>-2.565009988789676</v>
       </c>
       <c r="G13">
-        <v>-10.02661069891251</v>
+        <v>-9.99534259629409</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-10.9688498747408</v>
       </c>
       <c r="E14">
-        <v>-15.14042508989454</v>
+        <v>-17.47930945927216</v>
       </c>
       <c r="F14">
-        <v>-1.920096972851163</v>
+        <v>-2.323459710868146</v>
       </c>
       <c r="G14">
-        <v>-9.628891689461085</v>
+        <v>-9.671895676016216</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-10.68156717246178</v>
       </c>
       <c r="E15">
-        <v>-17.20549980687238</v>
+        <v>-17.80866537385003</v>
       </c>
       <c r="F15">
-        <v>-2.052808886086269</v>
+        <v>-2.07784214899887</v>
       </c>
       <c r="G15">
-        <v>-8.966484632508312</v>
+        <v>-9.376359965179939</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-10.37430939963934</v>
       </c>
       <c r="E16">
-        <v>-16.99823608001532</v>
+        <v>-19.2865011669352</v>
       </c>
       <c r="F16">
-        <v>-1.459055012577251</v>
+        <v>-1.942935890513748</v>
       </c>
       <c r="G16">
-        <v>-8.271140957985331</v>
+        <v>-8.289484690818433</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-10.05584832305872</v>
       </c>
       <c r="E17">
-        <v>-18.40620204763614</v>
+        <v>-20.01005621540676</v>
       </c>
       <c r="F17">
-        <v>-1.461189715374265</v>
+        <v>-1.837459040747884</v>
       </c>
       <c r="G17">
-        <v>-7.685594836817819</v>
+        <v>-8.306686285440486</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-9.738941847180664</v>
       </c>
       <c r="E18">
-        <v>-19.64481667279211</v>
+        <v>-20.63600000664298</v>
       </c>
       <c r="F18">
-        <v>-0.755392523697391</v>
+        <v>-0.9580782881817768</v>
       </c>
       <c r="G18">
-        <v>-7.669796913504417</v>
+        <v>-7.689938272565342</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-9.442856721213618</v>
       </c>
       <c r="E19">
-        <v>-21.01308150878769</v>
+        <v>-21.14099731408235</v>
       </c>
       <c r="F19">
-        <v>-0.6970158160873041</v>
+        <v>-0.757945552032819</v>
       </c>
       <c r="G19">
-        <v>-8.347127909748224</v>
+        <v>-8.078420859962199</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-9.171115110316817</v>
       </c>
       <c r="E20">
-        <v>-21.6850662952599</v>
+        <v>-22.14290407438339</v>
       </c>
       <c r="F20">
-        <v>-0.1481138956028649</v>
+        <v>-0.9471156739731281</v>
       </c>
       <c r="G20">
-        <v>-7.694986854512731</v>
+        <v>-7.606724399890222</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-8.943358000720551</v>
       </c>
       <c r="E21">
-        <v>-21.64359453029765</v>
+        <v>-23.46358823398037</v>
       </c>
       <c r="F21">
-        <v>-0.3569726539729127</v>
+        <v>-0.3581207711931928</v>
       </c>
       <c r="G21">
-        <v>-7.270012123636489</v>
+        <v>-8.01164053534402</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-8.74874451096562</v>
       </c>
       <c r="E22">
-        <v>-23.42556716621197</v>
+        <v>-23.4465430578155</v>
       </c>
       <c r="F22">
-        <v>0.0176697578216085</v>
+        <v>-0.5140692184442277</v>
       </c>
       <c r="G22">
-        <v>-7.62122458935223</v>
+        <v>-7.278798311497715</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-8.596257772463062</v>
       </c>
       <c r="E23">
-        <v>-22.14594720891654</v>
+        <v>-24.07685229799512</v>
       </c>
       <c r="F23">
-        <v>0.2255427589823248</v>
+        <v>-0.4252350981680088</v>
       </c>
       <c r="G23">
-        <v>-7.730290512143519</v>
+        <v>-7.166729723902306</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-8.467105185274823</v>
       </c>
       <c r="E24">
-        <v>-22.64277967772008</v>
+        <v>-24.45163333534393</v>
       </c>
       <c r="F24">
-        <v>0.7758645011951624</v>
+        <v>-0.2110416537239322</v>
       </c>
       <c r="G24">
-        <v>-7.011938546122604</v>
+        <v>-7.008545236944851</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-8.354808528454187</v>
       </c>
       <c r="E25">
-        <v>-24.07611868520588</v>
+        <v>-24.8628776454025</v>
       </c>
       <c r="F25">
-        <v>0.4045968581996464</v>
+        <v>-0.1797798963096817</v>
       </c>
       <c r="G25">
-        <v>-6.6384825249285</v>
+        <v>-7.670465643703349</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-8.241521051527759</v>
       </c>
       <c r="E26">
-        <v>-23.46611059400264</v>
+        <v>-24.70237041267463</v>
       </c>
       <c r="F26">
-        <v>0.6762193579450071</v>
+        <v>-0.01492649947855204</v>
       </c>
       <c r="G26">
-        <v>-7.379349511161998</v>
+        <v>-7.686905812851371</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-8.113836392120705</v>
       </c>
       <c r="E27">
-        <v>-24.30025550621552</v>
+        <v>-24.54139674712397</v>
       </c>
       <c r="F27">
-        <v>0.5647467849176804</v>
+        <v>-0.0458237752355708</v>
       </c>
       <c r="G27">
-        <v>-8.223147979302517</v>
+        <v>-7.611031419636814</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-7.963851679977881</v>
       </c>
       <c r="E28">
-        <v>-23.97023843443254</v>
+        <v>-25.58489301271145</v>
       </c>
       <c r="F28">
-        <v>0.9537514307419395</v>
+        <v>-0.1376549287751184</v>
       </c>
       <c r="G28">
-        <v>-8.015474147078496</v>
+        <v>-8.129525751451927</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-7.778688104552894</v>
       </c>
       <c r="E29">
-        <v>-23.99596016679611</v>
+        <v>-24.54439006844304</v>
       </c>
       <c r="F29">
-        <v>0.6861307739195032</v>
+        <v>-0.1328735921261597</v>
       </c>
       <c r="G29">
-        <v>-7.05683285418066</v>
+        <v>-7.235738045668414</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-7.565052831354888</v>
       </c>
       <c r="E30">
-        <v>-23.48299727357724</v>
+        <v>-24.30386469999964</v>
       </c>
       <c r="F30">
-        <v>0.3891229551153516</v>
+        <v>-0.2329163517296587</v>
       </c>
       <c r="G30">
-        <v>-8.172344347456862</v>
+        <v>-7.745740828175298</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-7.316830588953312</v>
       </c>
       <c r="E31">
-        <v>-24.41027478223187</v>
+        <v>-24.27498209277871</v>
       </c>
       <c r="F31">
-        <v>0.8428578865291696</v>
+        <v>-0.5901282566344728</v>
       </c>
       <c r="G31">
-        <v>-8.099091906309408</v>
+        <v>-7.787361006695015</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-7.051912731543096</v>
       </c>
       <c r="E32">
-        <v>-23.75552989630686</v>
+        <v>-24.12797876954172</v>
       </c>
       <c r="F32">
-        <v>0.3791676356685071</v>
+        <v>-0.3926653486247378</v>
       </c>
       <c r="G32">
-        <v>-7.842143914278875</v>
+        <v>-7.865172069050045</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-6.772965414394471</v>
       </c>
       <c r="E33">
-        <v>-25.00453736931044</v>
+        <v>-23.72128104738685</v>
       </c>
       <c r="F33">
-        <v>0.3628794474272605</v>
+        <v>-0.2654653920878597</v>
       </c>
       <c r="G33">
-        <v>-7.51538644846173</v>
+        <v>-7.2047314761476</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-6.496534887104187</v>
       </c>
       <c r="E34">
-        <v>-21.95379952829708</v>
+        <v>-23.56944584238367</v>
       </c>
       <c r="F34">
-        <v>0.6751068605230474</v>
+        <v>-0.699338558284754</v>
       </c>
       <c r="G34">
-        <v>-7.647636121664536</v>
+        <v>-7.204006466674501</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-6.229252172410239</v>
       </c>
       <c r="E35">
-        <v>-22.27033080448522</v>
+        <v>-22.87037172439758</v>
       </c>
       <c r="F35">
-        <v>-0.02914791104981396</v>
+        <v>-0.2245349303481333</v>
       </c>
       <c r="G35">
-        <v>-7.295029916276762</v>
+        <v>-6.862454172842352</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-5.980226277498525</v>
       </c>
       <c r="E36">
-        <v>-22.12050171346744</v>
+        <v>-23.47353276290121</v>
       </c>
       <c r="F36">
-        <v>0.05091297006335546</v>
+        <v>-0.6348095659740753</v>
       </c>
       <c r="G36">
-        <v>-7.601089851382382</v>
+        <v>-7.480400603202712</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-5.758631658681403</v>
       </c>
       <c r="E37">
-        <v>-20.63145341873928</v>
+        <v>-22.35122293568424</v>
       </c>
       <c r="F37">
-        <v>-0.2362919488960667</v>
+        <v>-0.6010817588016906</v>
       </c>
       <c r="G37">
-        <v>-6.781709967139528</v>
+        <v>-7.264317985308942</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-5.564729470044466</v>
       </c>
       <c r="E38">
-        <v>-20.87786127491865</v>
+        <v>-22.27326072716819</v>
       </c>
       <c r="F38">
-        <v>0.1342591562960277</v>
+        <v>-0.6666950840426339</v>
       </c>
       <c r="G38">
-        <v>-6.943006366903899</v>
+        <v>-6.649364288116084</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-5.40680364939077</v>
       </c>
       <c r="E39">
-        <v>-20.18514060596532</v>
+        <v>-22.00650643727236</v>
       </c>
       <c r="F39">
-        <v>-0.2484830319630671</v>
+        <v>-0.6169888980376496</v>
       </c>
       <c r="G39">
-        <v>-6.738500726760961</v>
+        <v>-6.455260382057536</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-5.275189056113939</v>
       </c>
       <c r="E40">
-        <v>-21.34591981987745</v>
+        <v>-22.25711671733084</v>
       </c>
       <c r="F40">
-        <v>-0.8295951905379623</v>
+        <v>-0.4946655404010522</v>
       </c>
       <c r="G40">
-        <v>-6.908202601649541</v>
+        <v>-6.940215577014293</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-5.173186606983069</v>
       </c>
       <c r="E41">
-        <v>-19.65947081468093</v>
+        <v>-21.00669183196286</v>
       </c>
       <c r="F41">
-        <v>-0.3389498643902039</v>
+        <v>-0.7837094349946893</v>
       </c>
       <c r="G41">
-        <v>-6.736236313612099</v>
+        <v>-6.207111820070385</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-5.087269626138396</v>
       </c>
       <c r="E42">
-        <v>-20.13372884055623</v>
+        <v>-20.84041985182323</v>
       </c>
       <c r="F42">
-        <v>-0.5082954976467152</v>
+        <v>-0.7080662372406495</v>
       </c>
       <c r="G42">
-        <v>-6.671472111227337</v>
+        <v>-6.459742860717709</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-5.014477713929351</v>
       </c>
       <c r="E43">
-        <v>-19.06708301584154</v>
+        <v>-20.21750560969814</v>
       </c>
       <c r="F43">
-        <v>-0.4124782401648964</v>
+        <v>-0.9588677223166446</v>
       </c>
       <c r="G43">
-        <v>-6.040826428178333</v>
+        <v>-6.690107172067894</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-4.94291504516064</v>
       </c>
       <c r="E44">
-        <v>-18.61213893160896</v>
+        <v>-19.3068747714957</v>
       </c>
       <c r="F44">
-        <v>-0.4119182638006039</v>
+        <v>-1.08689521788892</v>
       </c>
       <c r="G44">
-        <v>-6.569808568261858</v>
+        <v>-6.468439663849375</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-4.864168698085072</v>
       </c>
       <c r="E45">
-        <v>-17.84742005440767</v>
+        <v>-18.98011820099824</v>
       </c>
       <c r="F45">
-        <v>-0.8790735755071767</v>
+        <v>-0.7738560047383891</v>
       </c>
       <c r="G45">
-        <v>-6.329244466105178</v>
+        <v>-5.912830805993491</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-4.770604111242714</v>
       </c>
       <c r="E46">
-        <v>-17.35596741272525</v>
+        <v>-18.29217960059701</v>
       </c>
       <c r="F46">
-        <v>-0.5912341271172101</v>
+        <v>-0.849556359843222</v>
       </c>
       <c r="G46">
-        <v>-5.752818897898357</v>
+        <v>-6.623005724532407</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-4.653000292450234</v>
       </c>
       <c r="E47">
-        <v>-16.13622746723324</v>
+        <v>-18.186494074206</v>
       </c>
       <c r="F47">
-        <v>-1.083126974573585</v>
+        <v>-1.175835369192697</v>
       </c>
       <c r="G47">
-        <v>-5.032963944202613</v>
+        <v>-6.582421746766482</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-4.51257267518637</v>
       </c>
       <c r="E48">
-        <v>-17.42582365276757</v>
+        <v>-17.03027503361958</v>
       </c>
       <c r="F48">
-        <v>-0.6203769207150995</v>
+        <v>-1.261749494374047</v>
       </c>
       <c r="G48">
-        <v>-6.472409007950961</v>
+        <v>-5.949819531303768</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-4.344456106184526</v>
       </c>
       <c r="E49">
-        <v>-16.20221639047301</v>
+        <v>-17.395971952109</v>
       </c>
       <c r="F49">
-        <v>-1.206485791463681</v>
+        <v>-1.393613159388687</v>
       </c>
       <c r="G49">
-        <v>-5.523788736400499</v>
+        <v>-5.719971665057709</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-4.159116644272323</v>
       </c>
       <c r="E50">
-        <v>-15.60051352059985</v>
+        <v>-17.52078575270841</v>
       </c>
       <c r="F50">
-        <v>-1.013455477426326</v>
+        <v>-1.178695721834564</v>
       </c>
       <c r="G50">
-        <v>-6.061974193083198</v>
+        <v>-6.174913454155433</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-3.959524926338901</v>
       </c>
       <c r="E51">
-        <v>-15.37154934629802</v>
+        <v>-17.01784890094254</v>
       </c>
       <c r="F51">
-        <v>-0.7690812950286527</v>
+        <v>-1.38245587884038</v>
       </c>
       <c r="G51">
-        <v>-5.292977501402511</v>
+        <v>-5.90443195196036</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-3.759683528441503</v>
       </c>
       <c r="E52">
-        <v>-14.46506659028662</v>
+        <v>-16.16502403344802</v>
       </c>
       <c r="F52">
-        <v>-1.3381953801414</v>
+        <v>-1.276708981301204</v>
       </c>
       <c r="G52">
-        <v>-4.792515711139807</v>
+        <v>-6.252529194323647</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-3.568758396124887</v>
       </c>
       <c r="E53">
-        <v>-14.06451400736016</v>
+        <v>-15.15826274901076</v>
       </c>
       <c r="F53">
-        <v>-1.406293807590742</v>
+        <v>-1.663761993524467</v>
       </c>
       <c r="G53">
-        <v>-5.484843478676512</v>
+        <v>-6.428881955200623</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-3.399622771555134</v>
       </c>
       <c r="E54">
-        <v>-15.3158038312636</v>
+        <v>-15.13407616933579</v>
       </c>
       <c r="F54">
-        <v>-1.553220505457887</v>
+        <v>-1.472220255709943</v>
       </c>
       <c r="G54">
-        <v>-4.771348082961707</v>
+        <v>-7.12192480057381</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-3.265931010034544</v>
       </c>
       <c r="E55">
-        <v>-13.95943529648618</v>
+        <v>-14.55181856685156</v>
       </c>
       <c r="F55">
-        <v>-1.298668172782016</v>
+        <v>-1.577900883856896</v>
       </c>
       <c r="G55">
-        <v>-5.116634672162153</v>
+        <v>-6.527850714097135</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-3.175120147155759</v>
       </c>
       <c r="E56">
-        <v>-13.22823165541566</v>
+        <v>-14.11097162220485</v>
       </c>
       <c r="F56">
-        <v>-1.422208402133326</v>
+        <v>-2.038663684316065</v>
       </c>
       <c r="G56">
-        <v>-5.344850439457351</v>
+        <v>-6.888779630970637</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-3.14005816279737</v>
       </c>
       <c r="E57">
-        <v>-13.054265797937</v>
+        <v>-13.69470523447178</v>
       </c>
       <c r="F57">
-        <v>-1.248718446760609</v>
+        <v>-2.075762946817843</v>
       </c>
       <c r="G57">
-        <v>-5.854386435043198</v>
+        <v>-6.807403111069812</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-3.158961482425382</v>
       </c>
       <c r="E58">
-        <v>-13.54224962852954</v>
+        <v>-13.85521699567365</v>
       </c>
       <c r="F58">
-        <v>-1.467453829674235</v>
+        <v>-1.986163415061438</v>
       </c>
       <c r="G58">
-        <v>-6.686541714522099</v>
+        <v>-6.856395874505486</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-3.238318146125429</v>
       </c>
       <c r="E59">
-        <v>-11.29722693990891</v>
+        <v>-13.19497001382932</v>
       </c>
       <c r="F59">
-        <v>-1.738921424715272</v>
+        <v>-2.037337468104182</v>
       </c>
       <c r="G59">
-        <v>-5.899909746753716</v>
+        <v>-7.2007356476817</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-3.369316194994123</v>
       </c>
       <c r="E60">
-        <v>-11.94593084150769</v>
+        <v>-12.89630356760144</v>
       </c>
       <c r="F60">
-        <v>-1.757125626759194</v>
+        <v>-2.162482245114715</v>
       </c>
       <c r="G60">
-        <v>-6.259739562508179</v>
+        <v>-6.518303100761877</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-3.54802800591128</v>
       </c>
       <c r="E61">
-        <v>-11.16006851916459</v>
+        <v>-12.50733029271259</v>
       </c>
       <c r="F61">
-        <v>-1.888340680097441</v>
+        <v>-2.125764859985627</v>
       </c>
       <c r="G61">
-        <v>-6.48549228392216</v>
+        <v>-7.515350032460798</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-3.762230517412026</v>
       </c>
       <c r="E62">
-        <v>-10.66567689785119</v>
+        <v>-13.02581792422081</v>
       </c>
       <c r="F62">
-        <v>-2.054913767656783</v>
+        <v>-2.121153338654242</v>
       </c>
       <c r="G62">
-        <v>-6.717458899313353</v>
+        <v>-7.584835072784561</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-3.99925747434703</v>
       </c>
       <c r="E63">
-        <v>-11.27299054701986</v>
+        <v>-12.97786138447958</v>
       </c>
       <c r="F63">
-        <v>-1.622196173986794</v>
+        <v>-2.18951684367248</v>
       </c>
       <c r="G63">
-        <v>-7.669297021127987</v>
+        <v>-7.27350805972596</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-4.248137554760739</v>
       </c>
       <c r="E64">
-        <v>-10.44528059637188</v>
+        <v>-12.39227988207372</v>
       </c>
       <c r="F64">
-        <v>-2.519689179815112</v>
+        <v>-2.281837562347082</v>
       </c>
       <c r="G64">
-        <v>-7.180302960613318</v>
+        <v>-7.549713495158433</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-4.492056701243738</v>
       </c>
       <c r="E65">
-        <v>-10.03631410873917</v>
+        <v>-12.51016058896739</v>
       </c>
       <c r="F65">
-        <v>-2.005858678430398</v>
+        <v>-2.234733278354291</v>
       </c>
       <c r="G65">
-        <v>-6.930038960026573</v>
+        <v>-7.393690794438121</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-4.724133924662724</v>
       </c>
       <c r="E66">
-        <v>-10.20493636688878</v>
+        <v>-11.85914263715069</v>
       </c>
       <c r="F66">
-        <v>-1.623538129179329</v>
+        <v>-2.245180648038398</v>
       </c>
       <c r="G66">
-        <v>-7.822009176309027</v>
+        <v>-7.661000794006573</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-4.928949982658771</v>
       </c>
       <c r="E67">
-        <v>-10.7158071051161</v>
+        <v>-12.07934874272167</v>
       </c>
       <c r="F67">
-        <v>-2.088185972757628</v>
+        <v>-2.418084947657336</v>
       </c>
       <c r="G67">
-        <v>-7.440796546916411</v>
+        <v>-7.656005180787813</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-5.105248836979738</v>
       </c>
       <c r="E68">
-        <v>-10.18270608798513</v>
+        <v>-12.12867741008723</v>
       </c>
       <c r="F68">
-        <v>-2.375099306391264</v>
+        <v>-2.581960870953163</v>
       </c>
       <c r="G68">
-        <v>-7.236032684221409</v>
+        <v>-7.389473159421089</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-5.245072895754647</v>
       </c>
       <c r="E69">
-        <v>-11.55523674649593</v>
+        <v>-12.09725885742201</v>
       </c>
       <c r="F69">
-        <v>-2.476562716090565</v>
+        <v>-2.328990720016638</v>
       </c>
       <c r="G69">
-        <v>-7.798130211334264</v>
+        <v>-7.762574952242492</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-5.350931224345628</v>
       </c>
       <c r="E70">
-        <v>-9.96534386409096</v>
+        <v>-11.72211554215259</v>
       </c>
       <c r="F70">
-        <v>-2.065284099172429</v>
+        <v>-2.590305844168965</v>
       </c>
       <c r="G70">
-        <v>-7.38447754620233</v>
+        <v>-7.192906207481323</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-5.422791791594443</v>
       </c>
       <c r="E71">
-        <v>-10.76174394544991</v>
+        <v>-12.15059975275836</v>
       </c>
       <c r="F71">
-        <v>-2.137843285085847</v>
+        <v>-2.562824755581091</v>
       </c>
       <c r="G71">
-        <v>-7.622095262829058</v>
+        <v>-7.592340079522089</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-5.462814271080504</v>
       </c>
       <c r="E72">
-        <v>-10.98035149969619</v>
+        <v>-12.24881782551072</v>
       </c>
       <c r="F72">
-        <v>-2.508082095767086</v>
+        <v>-2.621387017489405</v>
       </c>
       <c r="G72">
-        <v>-6.612610611539095</v>
+        <v>-7.048824644521163</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-5.474338863812557</v>
       </c>
       <c r="E73">
-        <v>-10.74044653219183</v>
+        <v>-11.87587987708304</v>
       </c>
       <c r="F73">
-        <v>-2.589152756744268</v>
+        <v>-2.800726903460692</v>
       </c>
       <c r="G73">
-        <v>-7.059911661532182</v>
+        <v>-7.00727398745777</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-5.455539058042641</v>
       </c>
       <c r="E74">
-        <v>-10.52179822167949</v>
+        <v>-13.02642926821185</v>
       </c>
       <c r="F74">
-        <v>-3.048956307750995</v>
+        <v>-2.846249834081539</v>
       </c>
       <c r="G74">
-        <v>-6.828583981430069</v>
+        <v>-7.099479301817552</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-5.411214010659985</v>
       </c>
       <c r="E75">
-        <v>-11.81818711822532</v>
+        <v>-12.79283246500018</v>
       </c>
       <c r="F75">
-        <v>-2.609316876063213</v>
+        <v>-2.794596984679976</v>
       </c>
       <c r="G75">
-        <v>-6.394750230690737</v>
+        <v>-6.671541632683661</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-5.338427694529742</v>
       </c>
       <c r="E76">
-        <v>-11.41708658994393</v>
+        <v>-13.19780936703213</v>
       </c>
       <c r="F76">
-        <v>-2.959972252974869</v>
+        <v>-3.168108674969676</v>
       </c>
       <c r="G76">
-        <v>-6.261232618546391</v>
+        <v>-6.724626230405875</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-5.248565498779205</v>
       </c>
       <c r="E77">
-        <v>-12.36955599950323</v>
+        <v>-13.34761128720586</v>
       </c>
       <c r="F77">
-        <v>-3.024545977125299</v>
+        <v>-2.854222870333484</v>
       </c>
       <c r="G77">
-        <v>-6.644977815276549</v>
+        <v>-6.8076381598031</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-5.142499252488859</v>
       </c>
       <c r="E78">
-        <v>-11.73129475896614</v>
+        <v>-14.09774847810245</v>
       </c>
       <c r="F78">
-        <v>-2.876935047783441</v>
+        <v>-3.320531590554396</v>
       </c>
       <c r="G78">
-        <v>-6.102141042111175</v>
+        <v>-6.783580425369216</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-5.029318709932906</v>
       </c>
       <c r="E79">
-        <v>-13.64911255816255</v>
+        <v>-15.16552642131906</v>
       </c>
       <c r="F79">
-        <v>-3.259911664017528</v>
+        <v>-3.398586165817985</v>
       </c>
       <c r="G79">
-        <v>-5.893364798222576</v>
+        <v>-6.392595065544671</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-4.907951477727218</v>
       </c>
       <c r="E80">
-        <v>-12.79469366781733</v>
+        <v>-15.33561137657315</v>
       </c>
       <c r="F80">
-        <v>-3.13236544990628</v>
+        <v>-3.590521378148839</v>
       </c>
       <c r="G80">
-        <v>-5.256925660479848</v>
+        <v>-6.071624433330173</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-4.779640522151892</v>
       </c>
       <c r="E81">
-        <v>-13.45123182944938</v>
+        <v>-15.58728131954943</v>
       </c>
       <c r="F81">
-        <v>-3.106195666917038</v>
+        <v>-3.34300022798793</v>
       </c>
       <c r="G81">
-        <v>-5.340894337537923</v>
+        <v>-6.173496540664626</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-4.642439391209759</v>
       </c>
       <c r="E82">
-        <v>-14.82105446050359</v>
+        <v>-16.62134930225294</v>
       </c>
       <c r="F82">
-        <v>-3.386527621535433</v>
+        <v>-3.342041806902891</v>
       </c>
       <c r="G82">
-        <v>-5.176628378424825</v>
+        <v>-6.250321060448953</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-4.492818281389294</v>
       </c>
       <c r="E83">
-        <v>-15.66849044392898</v>
+        <v>-16.94441063796015</v>
       </c>
       <c r="F83">
-        <v>-2.888878448997005</v>
+        <v>-3.775440318577981</v>
       </c>
       <c r="G83">
-        <v>-5.281142301099616</v>
+        <v>-5.899085420914437</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-4.334530029723409</v>
       </c>
       <c r="E84">
-        <v>-17.00658658608546</v>
+        <v>-18.55621680608823</v>
       </c>
       <c r="F84">
-        <v>-3.615041053271704</v>
+        <v>-3.671127325013051</v>
       </c>
       <c r="G84">
-        <v>-5.541847762317222</v>
+        <v>-6.085998822061688</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-4.165828367175499</v>
       </c>
       <c r="E85">
-        <v>-18.60842558292267</v>
+        <v>-19.00590786047192</v>
       </c>
       <c r="F85">
-        <v>-3.185852304737641</v>
+        <v>-3.774014698277763</v>
       </c>
       <c r="G85">
-        <v>-4.196614203525455</v>
+        <v>-5.269661329169424</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-4.000738777795001</v>
       </c>
       <c r="E86">
-        <v>-17.75932312106245</v>
+        <v>-20.68679137111301</v>
       </c>
       <c r="F86">
-        <v>-3.564832048253221</v>
+        <v>-3.905962028400085</v>
       </c>
       <c r="G86">
-        <v>-4.494195831505002</v>
+        <v>-5.043574242655977</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-3.843094627194367</v>
       </c>
       <c r="E87">
-        <v>-20.52069600145968</v>
+        <v>-22.26762730550264</v>
       </c>
       <c r="F87">
-        <v>-3.921978512133213</v>
+        <v>-3.931087240094397</v>
       </c>
       <c r="G87">
-        <v>-4.841223767659104</v>
+        <v>-5.418089638422647</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-3.709882457848094</v>
       </c>
       <c r="E88">
-        <v>-21.5483924212344</v>
+        <v>-23.08065594341776</v>
       </c>
       <c r="F88">
-        <v>-3.741856647333683</v>
+        <v>-3.785722014781528</v>
       </c>
       <c r="G88">
-        <v>-4.57783014346361</v>
+        <v>-4.933465498019817</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-3.610320276418557</v>
       </c>
       <c r="E89">
-        <v>-23.07008648508386</v>
+        <v>-25.0309655436192</v>
       </c>
       <c r="F89">
-        <v>-3.612997470888998</v>
+        <v>-3.969642772490297</v>
       </c>
       <c r="G89">
-        <v>-4.735935177328123</v>
+        <v>-5.516760448220626</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-3.558633803782392</v>
       </c>
       <c r="E90">
-        <v>-25.39742777421592</v>
+        <v>-26.36594156718439</v>
       </c>
       <c r="F90">
-        <v>-3.588044559614469</v>
+        <v>-4.05222271887538</v>
       </c>
       <c r="G90">
-        <v>-4.307977644920998</v>
+        <v>-5.298284305901963</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-3.568391425451258</v>
       </c>
       <c r="E91">
-        <v>-26.17658795502767</v>
+        <v>-28.45518022146716</v>
       </c>
       <c r="F91">
-        <v>-3.62497897700309</v>
+        <v>-3.949658408897759</v>
       </c>
       <c r="G91">
-        <v>-4.247222513184293</v>
+        <v>-5.740831412500657</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-3.645672770276467</v>
       </c>
       <c r="E92">
-        <v>-29.22414680728764</v>
+        <v>-30.02082765403506</v>
       </c>
       <c r="F92">
-        <v>-3.433393335716218</v>
+        <v>-3.845023180413139</v>
       </c>
       <c r="G92">
-        <v>-5.599921352167118</v>
+        <v>-5.472243542354046</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-3.803695776648971</v>
       </c>
       <c r="E93">
-        <v>-31.30456399420346</v>
+        <v>-32.96199000948482</v>
       </c>
       <c r="F93">
-        <v>-4.092039026458341</v>
+        <v>-3.887297254080206</v>
       </c>
       <c r="G93">
-        <v>-5.150547900666447</v>
+        <v>-5.869187884149279</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-4.03768293812476</v>
       </c>
       <c r="E94">
-        <v>-32.39946523248901</v>
+        <v>-34.37762041936362</v>
       </c>
       <c r="F94">
-        <v>-3.88796988841128</v>
+        <v>-4.125143072976417</v>
       </c>
       <c r="G94">
-        <v>-5.147601515136495</v>
+        <v>-6.285667755171751</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-4.35462754407869</v>
       </c>
       <c r="E95">
-        <v>-34.17824529422792</v>
+        <v>-35.83678304987816</v>
       </c>
       <c r="F95">
-        <v>-3.827049264507196</v>
+        <v>-3.775205062235586</v>
       </c>
       <c r="G95">
-        <v>-5.729251124204286</v>
+        <v>-6.720497980118404</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-4.747865267727843</v>
       </c>
       <c r="E96">
-        <v>-37.03113863432017</v>
+        <v>-38.63976807793188</v>
       </c>
       <c r="F96">
-        <v>-4.197091752113971</v>
+        <v>-3.837353326630619</v>
       </c>
       <c r="G96">
-        <v>-6.593260472862055</v>
+        <v>-6.486799949410172</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-5.207567188788719</v>
       </c>
       <c r="E97">
-        <v>-39.47166233856294</v>
+        <v>-41.3242655835749</v>
       </c>
       <c r="F97">
-        <v>-3.963246947773282</v>
+        <v>-4.054464281067355</v>
       </c>
       <c r="G97">
-        <v>-6.701022040710871</v>
+        <v>-7.621102099167277</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-5.733825645774115</v>
       </c>
       <c r="E98">
-        <v>-41.00168426611251</v>
+        <v>-42.74085376570632</v>
       </c>
       <c r="F98">
-        <v>-3.510404168052279</v>
+        <v>-3.755962087468554</v>
       </c>
       <c r="G98">
-        <v>-6.731829977499329</v>
+        <v>-7.906106964643134</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-6.29144030586705</v>
       </c>
       <c r="E99">
-        <v>-43.87891815399598</v>
+        <v>-46.23497902528469</v>
       </c>
       <c r="F99">
-        <v>-4.02125420352172</v>
+        <v>-3.607037367425856</v>
       </c>
       <c r="G99">
-        <v>-7.456395837497457</v>
+        <v>-7.928916623408712</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-6.900459914592512</v>
       </c>
       <c r="E100">
-        <v>-46.23814669285306</v>
+        <v>-47.88958606549627</v>
       </c>
       <c r="F100">
-        <v>-3.737635287049017</v>
+        <v>-4.005258428973661</v>
       </c>
       <c r="G100">
-        <v>-8.372830985315124</v>
+        <v>-8.74414839409086</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-7.485576777001643</v>
       </c>
       <c r="E101">
-        <v>-49.07651721680271</v>
+        <v>-49.89749898719379</v>
       </c>
       <c r="F101">
-        <v>-3.486311102141856</v>
+        <v>-3.804213660314222</v>
       </c>
       <c r="G101">
-        <v>-8.020691566848388</v>
+        <v>-8.764369206244728</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-8.12792703240501</v>
       </c>
       <c r="E102">
-        <v>-50.7297668469305</v>
+        <v>-52.99157092810505</v>
       </c>
       <c r="F102">
-        <v>-3.881657728801947</v>
+        <v>-3.604699714615155</v>
       </c>
       <c r="G102">
-        <v>-9.531872841887203</v>
+        <v>-8.93983143037164</v>
       </c>
     </row>
   </sheetData>
